--- a/data/trans_orig/P19-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2007</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129169</t>
+          <t>131350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>171138</t>
+          <t>172995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109743</t>
+          <t>108353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>142118</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>251237</t>
+          <t>247121</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>304586</t>
+          <t>303172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302638</t>
+          <t>300781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344607</t>
+          <t>342426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164562</t>
+          <t>163675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196937</t>
+          <t>198327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>475871</t>
+          <t>477285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529220</t>
+          <t>533336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,34%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95627</t>
+          <t>97309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133945</t>
+          <t>133289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131173</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167440</t>
+          <t>167399</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>235369</t>
+          <t>236293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>290456</t>
+          <t>288850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>232989</t>
+          <t>233645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>271307</t>
+          <t>269625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204425</t>
+          <t>204466</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240692</t>
+          <t>243088</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>448343</t>
+          <t>449949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>503430</t>
+          <t>502506</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114821</t>
+          <t>114234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154619</t>
+          <t>154510</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39602</t>
+          <t>39335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63592</t>
+          <t>62719</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>161721</t>
+          <t>162601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206775</t>
+          <t>206424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387770</t>
+          <t>387879</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>427568</t>
+          <t>428155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104190</t>
+          <t>105063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128180</t>
+          <t>128447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>503396</t>
+          <t>503747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>548450</t>
+          <t>547570</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252142</t>
+          <t>248367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>308134</t>
+          <t>307118</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205205</t>
+          <t>204608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259013</t>
+          <t>254436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>467728</t>
+          <t>470048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>548736</t>
+          <t>550725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>929288</t>
+          <t>930304</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>985280</t>
+          <t>989055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>455272</t>
+          <t>459849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>509080</t>
+          <t>509677</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1402972</t>
+          <t>1400983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1483980</t>
+          <t>1481660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51582</t>
+          <t>51940</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79990</t>
+          <t>79779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151248</t>
+          <t>150711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>194667</t>
+          <t>197888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214239</t>
+          <t>211223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>265826</t>
+          <t>262885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270565</t>
+          <t>270776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>298973</t>
+          <t>298615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>374085</t>
+          <t>370864</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>417504</t>
+          <t>418041</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>653481</t>
+          <t>656422</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>705068</t>
+          <t>708084</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57869</t>
+          <t>57620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86114</t>
+          <t>86783</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>302463</t>
+          <t>302138</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>361307</t>
+          <t>361562</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>367280</t>
+          <t>364654</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>432800</t>
+          <t>434502</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212087</t>
+          <t>211418</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240332</t>
+          <t>240581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>886528</t>
+          <t>886273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>945372</t>
+          <t>945697</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1113235</t>
+          <t>1111533</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1178755</t>
+          <t>1181381</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,41%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>761446</t>
+          <t>760983</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>862448</t>
+          <t>861321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1007923</t>
+          <t>1003473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1116332</t>
+          <t>1109676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1796375</t>
+          <t>1797629</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1945408</t>
+          <t>1944819</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2406830</t>
+          <t>2407957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2507832</t>
+          <t>2508295</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2260867</t>
+          <t>2267523</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2369276</t>
+          <t>2373726</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4701069</t>
+          <t>4701658</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4850102</t>
+          <t>4848848</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,95%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2012</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133939</t>
+          <t>134698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>175084</t>
+          <t>179070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101865</t>
+          <t>101082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137599</t>
+          <t>137370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>244778</t>
+          <t>245240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>301521</t>
+          <t>301806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262127</t>
+          <t>258141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>303272</t>
+          <t>302513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>176855</t>
+          <t>177084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212589</t>
+          <t>213372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>450144</t>
+          <t>449859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>506887</t>
+          <t>506425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119019</t>
+          <t>117124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161453</t>
+          <t>160694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116421</t>
+          <t>118481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155548</t>
+          <t>156572</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249354</t>
+          <t>249519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>306435</t>
+          <t>305452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,41%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>257344</t>
+          <t>258103</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299778</t>
+          <t>301673</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>181499</t>
+          <t>180475</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>220626</t>
+          <t>218566</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>449409</t>
+          <t>450392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506490</t>
+          <t>506325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114286</t>
+          <t>113795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155524</t>
+          <t>156276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80862</t>
+          <t>79223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110803</t>
+          <t>111964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201517</t>
+          <t>200142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255095</t>
+          <t>257374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471378</t>
+          <t>470626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512616</t>
+          <t>513107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149326</t>
+          <t>148165</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179267</t>
+          <t>180906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631936</t>
+          <t>629657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>685514</t>
+          <t>686889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>192304</t>
+          <t>190685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248215</t>
+          <t>247241</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185892</t>
+          <t>188262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238212</t>
+          <t>239050</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>394977</t>
+          <t>397061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>471477</t>
+          <t>471041</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>910794</t>
+          <t>911768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>966705</t>
+          <t>968324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>528445</t>
+          <t>527607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>580765</t>
+          <t>578395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1454190</t>
+          <t>1454626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1530690</t>
+          <t>1528606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86912</t>
+          <t>86847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123938</t>
+          <t>123780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190570</t>
+          <t>194316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>245035</t>
+          <t>244080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>293594</t>
+          <t>292978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>356417</t>
+          <t>358067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386658</t>
+          <t>386816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>423684</t>
+          <t>423749</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>516487</t>
+          <t>517442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>570952</t>
+          <t>567206</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>915701</t>
+          <t>914051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>978524</t>
+          <t>979140</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74956</t>
+          <t>74849</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>104699</t>
+          <t>106420</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>265593</t>
+          <t>264791</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>327307</t>
+          <t>323491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>353301</t>
+          <t>350892</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>427248</t>
+          <t>421698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162183</t>
+          <t>160462</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191926</t>
+          <t>192033</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>782044</t>
+          <t>785860</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>843758</t>
+          <t>844560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>948985</t>
+          <t>954535</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1022932</t>
+          <t>1025341</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,5%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>789550</t>
+          <t>788848</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>895597</t>
+          <t>889403</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1023772</t>
+          <t>1024076</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1136633</t>
+          <t>1134406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1843983</t>
+          <t>1841524</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1997615</t>
+          <t>1998242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2523800</t>
+          <t>2529994</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2629847</t>
+          <t>2630549</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2412528</t>
+          <t>2414755</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2525389</t>
+          <t>2525085</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4970943</t>
+          <t>4970316</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5124575</t>
+          <t>5127034</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2016</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130540</t>
+          <t>129853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169197</t>
+          <t>170113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126835</t>
+          <t>126857</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164131</t>
+          <t>162915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>267792</t>
+          <t>269957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>324169</t>
+          <t>324922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259895</t>
+          <t>258979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>298552</t>
+          <t>299239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182924</t>
+          <t>184140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220220</t>
+          <t>220198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>451978</t>
+          <t>451225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>508355</t>
+          <t>506190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,22%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103338</t>
+          <t>102319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139447</t>
+          <t>139675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138980</t>
+          <t>138942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177199</t>
+          <t>176910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>252825</t>
+          <t>251649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>302700</t>
+          <t>305498</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,76%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>237780</t>
+          <t>237552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>273889</t>
+          <t>274908</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195074</t>
+          <t>195363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>233293</t>
+          <t>233331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>446800</t>
+          <t>444002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>496675</t>
+          <t>497851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,42%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121055</t>
+          <t>119861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161606</t>
+          <t>162433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44403</t>
+          <t>45893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70441</t>
+          <t>70061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174765</t>
+          <t>175600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224153</t>
+          <t>225732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>360308</t>
+          <t>359481</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>400859</t>
+          <t>402053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95682</t>
+          <t>96062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121720</t>
+          <t>120230</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>463883</t>
+          <t>462304</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>513271</t>
+          <t>512436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>272406</t>
+          <t>276175</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>334408</t>
+          <t>335201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>265287</t>
+          <t>263376</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>318649</t>
+          <t>320731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>552524</t>
+          <t>555046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>637877</t>
+          <t>638352</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>815230</t>
+          <t>814437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877232</t>
+          <t>873463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>507227</t>
+          <t>505145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>560589</t>
+          <t>562500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1337637</t>
+          <t>1337162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1422990</t>
+          <t>1420468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>128579</t>
+          <t>128280</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173412</t>
+          <t>172662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203232</t>
+          <t>202489</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252964</t>
+          <t>252508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344103</t>
+          <t>345209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>410071</t>
+          <t>412080</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>447294</t>
+          <t>448044</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>492127</t>
+          <t>492426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>485280</t>
+          <t>485736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535012</t>
+          <t>535755</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>948879</t>
+          <t>946870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1014847</t>
+          <t>1013741</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104073</t>
+          <t>102637</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>137202</t>
+          <t>136796</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>309450</t>
+          <t>309516</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>374861</t>
+          <t>374324</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>423210</t>
+          <t>422259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>497070</t>
+          <t>492570</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149943</t>
+          <t>150349</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183072</t>
+          <t>184508</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>707164</t>
+          <t>707701</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>772575</t>
+          <t>772509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>872100</t>
+          <t>876600</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>945960</t>
+          <t>946911</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>932389</t>
+          <t>928138</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1038567</t>
+          <t>1034334</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1166928</t>
+          <t>1168642</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1275448</t>
+          <t>1280684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2135411</t>
+          <t>2118211</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2288053</t>
+          <t>2280941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2347155</t>
+          <t>2351388</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2453333</t>
+          <t>2457584</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2256148</t>
+          <t>2250912</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2364668</t>
+          <t>2362954</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4629265</t>
+          <t>4636377</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4781907</t>
+          <t>4799107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2023</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2023 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>163081</t>
+          <t>164127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>207322</t>
+          <t>209883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>187878</t>
+          <t>186182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223111</t>
+          <t>221813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>360676</t>
+          <t>360948</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>419685</t>
+          <t>418500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>293152</t>
+          <t>290591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>337393</t>
+          <t>336347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>223692</t>
+          <t>224990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258925</t>
+          <t>260621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>527592</t>
+          <t>528777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586601</t>
+          <t>586329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117572</t>
+          <t>119551</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158410</t>
+          <t>157200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144640</t>
+          <t>144076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176901</t>
+          <t>177562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>273287</t>
+          <t>273246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325792</t>
+          <t>323783</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>291356</t>
+          <t>292566</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>332194</t>
+          <t>330215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202119</t>
+          <t>201458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234380</t>
+          <t>234944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>502994</t>
+          <t>505003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>555499</t>
+          <t>555540</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>52905</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>210025</t>
+          <t>216014</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42492</t>
+          <t>42919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61406</t>
+          <t>62840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74837</t>
+          <t>64392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266946</t>
+          <t>262125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>456035</t>
+          <t>450046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622235</t>
+          <t>613155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104887</t>
+          <t>103453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123801</t>
+          <t>123374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>565406</t>
+          <t>570227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>757515</t>
+          <t>767960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>201655</t>
+          <t>197812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>257566</t>
+          <t>256016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145383</t>
+          <t>150974</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>358658</t>
+          <t>354480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>358894</t>
+          <t>315454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>574264</t>
+          <t>572541</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>771583</t>
+          <t>773133</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>827494</t>
+          <t>831337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>614610</t>
+          <t>618788</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>827885</t>
+          <t>822294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1428152</t>
+          <t>1429875</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1643522</t>
+          <t>1686962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>84,25%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69463</t>
+          <t>71125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112724</t>
+          <t>111321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155283</t>
+          <t>149437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>276328</t>
+          <t>267453</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>243717</t>
+          <t>240097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>375047</t>
+          <t>368756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>359044</t>
+          <t>360447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>402305</t>
+          <t>400643</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>554451</t>
+          <t>563326</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>675496</t>
+          <t>681342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>927500</t>
+          <t>933791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1058830</t>
+          <t>1062450</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52279</t>
+          <t>51770</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>100096</t>
+          <t>102628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>147326</t>
+          <t>149670</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>192320</t>
+          <t>193766</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>212866</t>
+          <t>214378</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>281594</t>
+          <t>280324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>139335</t>
+          <t>136803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187152</t>
+          <t>187661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>558102</t>
+          <t>556656</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>603096</t>
+          <t>600752</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>708260</t>
+          <t>709530</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>776988</t>
+          <t>775476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>648106</t>
+          <t>630880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>933704</t>
+          <t>928120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>825161</t>
+          <t>874242</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1158844</t>
+          <t>1169247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1647763</t>
+          <t>1623178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2061292</t>
+          <t>2047440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2422943</t>
+          <t>2428527</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2708541</t>
+          <t>2725767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2387741</t>
+          <t>2377338</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2721424</t>
+          <t>2672343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4841941</t>
+          <t>4855793</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5255470</t>
+          <t>5280055</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131350</t>
+          <t>129193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172995</t>
+          <t>172926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>108353</t>
+          <t>108619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>143005</t>
+          <t>143203</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247121</t>
+          <t>250548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303172</t>
+          <t>301555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300781</t>
+          <t>300850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>342426</t>
+          <t>344583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>163675</t>
+          <t>163477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198327</t>
+          <t>198061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>477285</t>
+          <t>478902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>533336</t>
+          <t>529909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97309</t>
+          <t>95842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133289</t>
+          <t>133240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>128777</t>
+          <t>127573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167399</t>
+          <t>166778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>236293</t>
+          <t>241096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288850</t>
+          <t>292526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>233645</t>
+          <t>233694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269625</t>
+          <t>271092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204466</t>
+          <t>205087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>243088</t>
+          <t>244292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>449949</t>
+          <t>446273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>502506</t>
+          <t>497703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114234</t>
+          <t>112071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154510</t>
+          <t>152865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39335</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62719</t>
+          <t>64946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162601</t>
+          <t>160661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206424</t>
+          <t>208728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387879</t>
+          <t>389524</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>428155</t>
+          <t>430318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105063</t>
+          <t>102836</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128447</t>
+          <t>127716</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>503747</t>
+          <t>501443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>547570</t>
+          <t>549510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>248367</t>
+          <t>250626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>307118</t>
+          <t>309619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>204608</t>
+          <t>205318</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254436</t>
+          <t>255981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>470048</t>
+          <t>472582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>550725</t>
+          <t>550500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>930304</t>
+          <t>927803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>989055</t>
+          <t>986796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>459849</t>
+          <t>458304</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>509677</t>
+          <t>508967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1400983</t>
+          <t>1401208</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1481660</t>
+          <t>1479126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51940</t>
+          <t>51338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79779</t>
+          <t>80788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>150711</t>
+          <t>150703</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197888</t>
+          <t>195764</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211223</t>
+          <t>210426</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>262885</t>
+          <t>263998</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270776</t>
+          <t>269767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>298615</t>
+          <t>299217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>370864</t>
+          <t>372988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>418041</t>
+          <t>418049</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>656422</t>
+          <t>655309</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>708084</t>
+          <t>708881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57620</t>
+          <t>58124</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86783</t>
+          <t>86811</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>302138</t>
+          <t>299294</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>361562</t>
+          <t>364907</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>364654</t>
+          <t>370695</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>434502</t>
+          <t>438401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211418</t>
+          <t>211390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240581</t>
+          <t>240077</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>886273</t>
+          <t>882928</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>945697</t>
+          <t>948541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1111533</t>
+          <t>1107634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1181381</t>
+          <t>1175340</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,02%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>760983</t>
+          <t>767221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>861321</t>
+          <t>868321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1003473</t>
+          <t>1007194</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1109676</t>
+          <t>1116436</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1797629</t>
+          <t>1799602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1944819</t>
+          <t>1942398</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2407957</t>
+          <t>2400957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2508295</t>
+          <t>2502057</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2267523</t>
+          <t>2260763</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2373726</t>
+          <t>2370005</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4701658</t>
+          <t>4704079</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4848848</t>
+          <t>4846875</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,92%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134698</t>
+          <t>133580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179070</t>
+          <t>176542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101082</t>
+          <t>102674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137370</t>
+          <t>139100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>245240</t>
+          <t>246690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>301806</t>
+          <t>301453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258141</t>
+          <t>260669</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>302513</t>
+          <t>303631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177084</t>
+          <t>175354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>213372</t>
+          <t>211780</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>449859</t>
+          <t>450212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>506425</t>
+          <t>504975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117124</t>
+          <t>118997</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>160694</t>
+          <t>159070</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118481</t>
+          <t>118243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156572</t>
+          <t>156559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249519</t>
+          <t>245569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>305452</t>
+          <t>304381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>258103</t>
+          <t>259727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>301673</t>
+          <t>299800</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180475</t>
+          <t>180488</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>218566</t>
+          <t>218804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>450392</t>
+          <t>451463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506325</t>
+          <t>510275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,51%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113795</t>
+          <t>115471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156276</t>
+          <t>156142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79223</t>
+          <t>79833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111964</t>
+          <t>110945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200142</t>
+          <t>201457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257374</t>
+          <t>258550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>470626</t>
+          <t>470760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513107</t>
+          <t>511431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148165</t>
+          <t>149184</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180906</t>
+          <t>180296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629657</t>
+          <t>628481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686889</t>
+          <t>685574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190685</t>
+          <t>194801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247241</t>
+          <t>246282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>188262</t>
+          <t>187458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>239050</t>
+          <t>237899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>397061</t>
+          <t>397477</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>471041</t>
+          <t>469495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>911768</t>
+          <t>912727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>968324</t>
+          <t>964208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>527607</t>
+          <t>528758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>578395</t>
+          <t>579199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1454626</t>
+          <t>1456172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1528606</t>
+          <t>1528190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86847</t>
+          <t>86983</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123780</t>
+          <t>123701</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>194316</t>
+          <t>193209</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>244080</t>
+          <t>244850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>292978</t>
+          <t>289644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>358067</t>
+          <t>354992</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386816</t>
+          <t>386895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>423749</t>
+          <t>423613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>517442</t>
+          <t>516672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>567206</t>
+          <t>568313</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>914051</t>
+          <t>917126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>979140</t>
+          <t>982474</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74849</t>
+          <t>74953</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106420</t>
+          <t>106157</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,82 +5098,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>39,78%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>296117</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>265565</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>324268</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>26,69%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>23,94%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>29,23%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>386068</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>352326</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>417896</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>28,05%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>39,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>296117</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>264791</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>323491</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>26,69%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>23,87%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>29,16%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>386068</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>350892</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>421698</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>28,05%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160462</t>
+          <t>160725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192033</t>
+          <t>191929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,82 +5211,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>71,92%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>813234</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>785083</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>843786</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>73,31%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>70,77%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>76,06%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>990165</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>958337</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1023907</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>71,95%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>813234</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>785860</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>844560</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>73,31%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>70,84%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>76,13%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>990165</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>954535</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1025341</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>71,95%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>788848</t>
+          <t>789280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>889403</t>
+          <t>894593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1024076</t>
+          <t>1024956</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1134406</t>
+          <t>1135115</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1841524</t>
+          <t>1845315</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1998242</t>
+          <t>2000817</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2529994</t>
+          <t>2524804</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2630549</t>
+          <t>2630117</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2414755</t>
+          <t>2414046</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2525085</t>
+          <t>2524205</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4970316</t>
+          <t>4967741</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5127034</t>
+          <t>5123243</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129853</t>
+          <t>128613</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>170113</t>
+          <t>169603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126857</t>
+          <t>127767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162915</t>
+          <t>163408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>269957</t>
+          <t>267120</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>324922</t>
+          <t>324953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258979</t>
+          <t>259489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>299239</t>
+          <t>300479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>184140</t>
+          <t>183647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220198</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>451225</t>
+          <t>451194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>506190</t>
+          <t>509027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102319</t>
+          <t>102485</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139675</t>
+          <t>141436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138942</t>
+          <t>137006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176910</t>
+          <t>176041</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>251649</t>
+          <t>249628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>305498</t>
+          <t>307903</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>237552</t>
+          <t>235791</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>274908</t>
+          <t>274742</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195363</t>
+          <t>196232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>233331</t>
+          <t>235267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>444002</t>
+          <t>441597</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>497851</t>
+          <t>499872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119861</t>
+          <t>120340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162433</t>
+          <t>160673</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45893</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70061</t>
+          <t>70367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175600</t>
+          <t>171856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225732</t>
+          <t>222196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359481</t>
+          <t>361241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>402053</t>
+          <t>401574</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96062</t>
+          <t>95756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120230</t>
+          <t>121123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>462304</t>
+          <t>465840</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>512436</t>
+          <t>516180</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,02%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>276175</t>
+          <t>271783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>335201</t>
+          <t>333735</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>263376</t>
+          <t>262597</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>320731</t>
+          <t>317926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>555046</t>
+          <t>554641</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>638352</t>
+          <t>636458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>814437</t>
+          <t>815903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>873463</t>
+          <t>877855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>505145</t>
+          <t>507950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>562500</t>
+          <t>563279</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1337162</t>
+          <t>1339056</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1420468</t>
+          <t>1420873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>128280</t>
+          <t>128987</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172662</t>
+          <t>171882</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>202489</t>
+          <t>202465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252508</t>
+          <t>253195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>345209</t>
+          <t>344425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>412080</t>
+          <t>409983</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>448044</t>
+          <t>448824</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>492426</t>
+          <t>491719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>485736</t>
+          <t>485049</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535755</t>
+          <t>535779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>946870</t>
+          <t>948967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1013741</t>
+          <t>1014525</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,66%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>102637</t>
+          <t>102126</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>136796</t>
+          <t>136266</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>309516</t>
+          <t>310062</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>374324</t>
+          <t>372787</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>422259</t>
+          <t>425447</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>492570</t>
+          <t>498216</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>150349</t>
+          <t>150879</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>184508</t>
+          <t>185019</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>707701</t>
+          <t>709238</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>772509</t>
+          <t>771963</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>876600</t>
+          <t>870954</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>946911</t>
+          <t>943723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>928138</t>
+          <t>925395</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1034334</t>
+          <t>1034152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1168642</t>
+          <t>1163812</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1280684</t>
+          <t>1278238</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2118211</t>
+          <t>2121845</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2280941</t>
+          <t>2280564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2351388</t>
+          <t>2351570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2457584</t>
+          <t>2460327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2250912</t>
+          <t>2253358</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2362954</t>
+          <t>2367784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4636377</t>
+          <t>4636754</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4799107</t>
+          <t>4795473</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,33%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>186086</t>
+          <t>204500</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164127</t>
+          <t>182683</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>209883</t>
+          <t>230970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>204772</t>
+          <t>219386</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>186182</t>
+          <t>199957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221813</t>
+          <t>239653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>390857</t>
+          <t>423887</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>360948</t>
+          <t>394514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>418500</t>
+          <t>456547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>314388</t>
+          <t>340921</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290591</t>
+          <t>314451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>336347</t>
+          <t>362738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>242031</t>
+          <t>268316</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224990</t>
+          <t>248049</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260621</t>
+          <t>287745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>556420</t>
+          <t>609237</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>528777</t>
+          <t>576577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586329</t>
+          <t>638610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>500474</t>
+          <t>545421</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>500474</t>
+          <t>545421</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>500474</t>
+          <t>545421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446803</t>
+          <t>487702</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446803</t>
+          <t>487702</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446803</t>
+          <t>487702</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>947277</t>
+          <t>1033124</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>947277</t>
+          <t>1033124</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>947277</t>
+          <t>1033124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>137084</t>
+          <t>142824</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119551</t>
+          <t>123948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157200</t>
+          <t>164524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>160586</t>
+          <t>176680</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144076</t>
+          <t>159786</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177562</t>
+          <t>195780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>297670</t>
+          <t>319504</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>273246</t>
+          <t>292507</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323783</t>
+          <t>348736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>312682</t>
+          <t>337628</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>292566</t>
+          <t>315928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>330215</t>
+          <t>356504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>218434</t>
+          <t>241756</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201458</t>
+          <t>222656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234944</t>
+          <t>258650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>531116</t>
+          <t>579385</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>505003</t>
+          <t>550153</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>555540</t>
+          <t>606382</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>449766</t>
+          <t>480452</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>449766</t>
+          <t>480452</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>449766</t>
+          <t>480452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>379020</t>
+          <t>418436</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>379020</t>
+          <t>418436</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>379020</t>
+          <t>418436</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>828786</t>
+          <t>898889</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>828786</t>
+          <t>898889</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>828786</t>
+          <t>898889</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>128788</t>
+          <t>143014</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52905</t>
+          <t>123522</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216014</t>
+          <t>167060</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51956</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42919</t>
+          <t>48930</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>70693</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>180744</t>
+          <t>201940</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64392</t>
+          <t>181585</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>262125</t>
+          <t>227957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>537272</t>
+          <t>326189</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>450046</t>
+          <t>302143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613155</t>
+          <t>345681</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>114337</t>
+          <t>127894</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103453</t>
+          <t>116126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123374</t>
+          <t>137889</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>651608</t>
+          <t>454083</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>570227</t>
+          <t>428066</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>767960</t>
+          <t>474438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>72,32%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>666060</t>
+          <t>469203</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>666060</t>
+          <t>469203</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666060</t>
+          <t>469203</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166293</t>
+          <t>186819</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166293</t>
+          <t>186819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166293</t>
+          <t>186819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>832352</t>
+          <t>656023</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>832352</t>
+          <t>656023</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>832352</t>
+          <t>656023</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>226032</t>
+          <t>245940</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197812</t>
+          <t>216751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256016</t>
+          <t>274808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>274117</t>
+          <t>294310</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150974</t>
+          <t>270226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>354480</t>
+          <t>316655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>500148</t>
+          <t>540250</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>315454</t>
+          <t>499304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>572541</t>
+          <t>582614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>803117</t>
+          <t>878386</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>773133</t>
+          <t>849518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>831337</t>
+          <t>907575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>699151</t>
+          <t>561313</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>618788</t>
+          <t>538968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>822294</t>
+          <t>585397</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1502268</t>
+          <t>1439699</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1429875</t>
+          <t>1397335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1686962</t>
+          <t>1480645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>74,78%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1029149</t>
+          <t>1124326</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1029149</t>
+          <t>1124326</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1029149</t>
+          <t>1124326</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>973268</t>
+          <t>855623</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>973268</t>
+          <t>855623</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>973268</t>
+          <t>855623</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2002416</t>
+          <t>1979949</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2002416</t>
+          <t>1979949</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2002416</t>
+          <t>1979949</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>90095</t>
+          <t>93004</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71125</t>
+          <t>73836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111321</t>
+          <t>113636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>200251</t>
+          <t>187952</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149437</t>
+          <t>167916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>267453</t>
+          <t>209536</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>290345</t>
+          <t>280956</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>240097</t>
+          <t>253088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>368756</t>
+          <t>312094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>381673</t>
+          <t>471447</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>360447</t>
+          <t>450815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>400643</t>
+          <t>490615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>630528</t>
+          <t>633077</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>563326</t>
+          <t>611493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>681342</t>
+          <t>653113</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1012202</t>
+          <t>1104524</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>933791</t>
+          <t>1073386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1062450</t>
+          <t>1132392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>471768</t>
+          <t>564451</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>471768</t>
+          <t>564451</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>471768</t>
+          <t>564451</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>830779</t>
+          <t>821029</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>830779</t>
+          <t>821029</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>830779</t>
+          <t>821029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1302547</t>
+          <t>1385480</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1302547</t>
+          <t>1385480</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1302547</t>
+          <t>1385480</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>75466</t>
+          <t>72414</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>52501</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>102628</t>
+          <t>96189</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,27 +10383,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>169111</t>
+          <t>188209</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>149670</t>
+          <t>166232</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193766</t>
+          <t>214978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>244577</t>
+          <t>260623</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>214378</t>
+          <t>228978</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>280324</t>
+          <t>293078</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>163965</t>
+          <t>163716</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136803</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187661</t>
+          <t>183629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,22 +10496,22 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>581311</t>
+          <t>644321</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>556656</t>
+          <t>617552</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>600752</t>
+          <t>666298</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>745277</t>
+          <t>808037</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>709530</t>
+          <t>775582</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>775476</t>
+          <t>839682</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>239431</t>
+          <t>236130</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>750422</t>
+          <t>832530</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>750422</t>
+          <t>832530</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>750422</t>
+          <t>832530</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>989854</t>
+          <t>1068660</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>989854</t>
+          <t>1068660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>989854</t>
+          <t>1068660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>843550</t>
+          <t>901696</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>630880</t>
+          <t>844246</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>928120</t>
+          <t>960125</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1060792</t>
+          <t>1125462</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>874242</t>
+          <t>1074566</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1169247</t>
+          <t>1174476</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1904342</t>
+          <t>2027159</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1623178</t>
+          <t>1947424</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2047440</t>
+          <t>2101667</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2513097</t>
+          <t>2518288</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2428527</t>
+          <t>2459859</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2725767</t>
+          <t>2575738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2485793</t>
+          <t>2476678</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2377338</t>
+          <t>2427664</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2672343</t>
+          <t>2527574</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4998891</t>
+          <t>4994964</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4855793</t>
+          <t>4920456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5280055</t>
+          <t>5074699</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>72,27%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3356647</t>
+          <t>3419984</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3356647</t>
+          <t>3419984</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3356647</t>
+          <t>3419984</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3546585</t>
+          <t>3602140</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3546585</t>
+          <t>3602140</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3546585</t>
+          <t>3602140</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6903233</t>
+          <t>7022123</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6903233</t>
+          <t>7022123</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6903233</t>
+          <t>7022123</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
